--- a/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
+++ b/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
@@ -8,16 +8,11 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataSignature="AMtx7miM75aaQP2C048Ucqbz3dfwBNZH7g=="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>Name</t>
   </si>
@@ -34,6 +29,9 @@
     <t>StageKinds</t>
   </si>
   <si>
+    <t>StageMode</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -47,6 +45,9 @@
   </si>
   <si>
     <t>ChapterKinds</t>
+  </si>
+  <si>
+    <t>ChapterMode</t>
   </si>
   <si>
     <t>샘플 챕터 정보</t>
@@ -118,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -128,13 +129,13 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -352,8 +353,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="14.43"/>
-    <col customWidth="1" min="9" max="9" width="15.86"/>
+    <col customWidth="1" min="1" max="7" width="14.43"/>
+    <col customWidth="1" min="10" max="10" width="15.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -366,22 +367,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>0.0</v>
@@ -389,13 +393,15 @@
       <c r="D2" s="4">
         <v>0.0</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <v>0.0</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="4"/>
+      <c r="F2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -411,10 +417,11 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="6"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="6"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -1426,50 +1433,55 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="14.43"/>
-    <col customWidth="1" min="6" max="6" width="15.86"/>
+    <col customWidth="1" min="1" max="6" width="14.43"/>
+    <col customWidth="1" min="7" max="7" width="15.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="9">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4">
         <v>0.0</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="4">
         <v>0.0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="4">
         <v>0.0</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4"/>
+      <c r="F2" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -1485,7 +1497,8 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
-      <c r="W2" s="6"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="6"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>

--- a/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
+++ b/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Stage" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Chapter" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Level" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Stage" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Chapter" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>StageID</t>
+  </si>
+  <si>
+    <t>ChapterID</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -23,13 +33,7 @@
     <t>Replace</t>
   </si>
   <si>
-    <t>StageType</t>
-  </si>
-  <si>
-    <t>StageKinds</t>
-  </si>
-  <si>
-    <t>StageMode</t>
+    <t>LevelMode</t>
   </si>
   <si>
     <t>Description</t>
@@ -38,13 +42,13 @@
     <t>Sample</t>
   </si>
   <si>
-    <t>샘플 스테이지 정보</t>
+    <t>샘플 레벨 정보</t>
   </si>
   <si>
-    <t>ChapterType</t>
+    <t>StageMode</t>
   </si>
   <si>
-    <t>ChapterKinds</t>
+    <t>샘플 스테이지 정보</t>
   </si>
   <si>
     <t>ChapterMode</t>
@@ -63,11 +67,11 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font/>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -119,23 +123,36 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -149,6 +166,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -353,45 +374,131 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="14.43"/>
+    <col customWidth="1" min="4" max="8" width="14.43"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="8"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="6" width="14.43"/>
+    <col customWidth="1" min="7" max="7" width="15.43"/>
     <col customWidth="1" min="10" max="10" width="15.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="A2" s="10">
         <v>0.0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="B2" s="6">
         <v>0.0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="E2" s="5">
         <v>0.0</v>
@@ -399,29 +506,29 @@
       <c r="F2" s="5">
         <v>0.0</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="6"/>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="11"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -1426,79 +1533,75 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="7" width="15.86"/>
+    <col customWidth="1" min="1" max="5" width="14.43"/>
+    <col customWidth="1" min="6" max="6" width="15.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="A2" s="10">
         <v>0.0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5">
         <v>0.0</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="12">
         <v>0.0</v>
       </c>
-      <c r="F2" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="6"/>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="14"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>

--- a/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
+++ b/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -36,23 +36,41 @@
     <t>LevelMode</t>
   </si>
   <si>
+    <t>LevelKinds</t>
+  </si>
+  <si>
     <t>RewardKinds</t>
+  </si>
+  <si>
+    <t>TutorialKinds</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>StageMode</t>
+    <t>Sample</t>
   </si>
   <si>
-    <t>ChapterMode</t>
+    <t>샘플 레벨 정보</t>
+  </si>
+  <si>
+    <t>StageKinds</t>
+  </si>
+  <si>
+    <t>샘플 스테이지 정보</t>
+  </si>
+  <si>
+    <t>ChapterKinds</t>
+  </si>
+  <si>
+    <t>샘플 챕터 정보</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -62,6 +80,7 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -77,12 +96,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -306,7 +328,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="9" width="14.43"/>
+    <col customWidth="1" min="1" max="11" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -334,11 +356,51 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="15.0" customHeight="1"/>
+    <row r="2" ht="15.0" customHeight="1">
+      <c r="A2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="3" ht="15.0" customHeight="1"/>
     <row r="4" ht="15.0" customHeight="1"/>
     <row r="5" ht="15.0" customHeight="1"/>
@@ -1349,8 +1411,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="14.43"/>
-    <col customWidth="1" min="8" max="8" width="15.43"/>
+    <col customWidth="1" min="1" max="8" width="14.43"/>
+    <col customWidth="1" min="9" max="9" width="15.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1369,17 +1431,48 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" ht="15.0" customHeight="1"/>
+    <row r="2" ht="15.0" customHeight="1">
+      <c r="A2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="3" ht="15.0" customHeight="1"/>
     <row r="4" ht="15.0" customHeight="1"/>
     <row r="5" ht="15.0" customHeight="1"/>
@@ -2390,8 +2483,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="14.43"/>
-    <col customWidth="1" min="7" max="7" width="15.86"/>
+    <col customWidth="1" min="1" max="8" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -2407,17 +2499,45 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" ht="15.0" customHeight="1"/>
+    <row r="2" ht="15.0" customHeight="1">
+      <c r="A2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="3" ht="15.0" customHeight="1"/>
     <row r="4" ht="15.0" customHeight="1"/>
     <row r="5" ht="15.0" customHeight="1"/>

--- a/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
+++ b/Templates/Tables/EpisodeInfo/T_EpisodeInfoTable.xlsx
@@ -13,7 +13,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="19">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -24,13 +33,10 @@
     <t>ChapterID</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>NumTargets</t>
   </si>
   <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>Replace</t>
+    <t>UnlockNumTargets</t>
   </si>
   <si>
     <t>LevelMode</t>
@@ -328,7 +334,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="11" width="14.43"/>
+    <col customWidth="1" min="1" max="7" width="14.43"/>
+    <col customWidth="1" min="8" max="8" width="17.29"/>
+    <col customWidth="1" min="9" max="13" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -350,55 +358,67 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="D2" s="2">
         <v>0.0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E2" s="2">
         <v>0.0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="F2" s="2">
         <v>0.0</v>
       </c>
       <c r="G2" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>-1.0</v>
-      </c>
-      <c r="I2" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="3">
         <v>-1.0</v>
       </c>
       <c r="J2" s="2">
         <v>-1.0</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>12</v>
+      <c r="K2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1"/>
@@ -1411,8 +1431,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="14.43"/>
-    <col customWidth="1" min="9" max="9" width="15.43"/>
+    <col customWidth="1" min="1" max="6" width="14.43"/>
+    <col customWidth="1" min="7" max="7" width="17.29"/>
+    <col customWidth="1" min="8" max="10" width="14.43"/>
+    <col customWidth="1" min="11" max="11" width="15.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -1420,57 +1442,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="D2" s="2">
         <v>0.0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="2">
         <v>0.0</v>
       </c>
-      <c r="F2" s="2">
-        <v>-1.0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>-1.0</v>
+      <c r="F2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.0</v>
       </c>
       <c r="H2" s="2">
         <v>-1.0</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
+      <c r="I2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1"/>
@@ -2483,7 +2517,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="14.43"/>
+    <col customWidth="1" min="1" max="5" width="14.43"/>
+    <col customWidth="1" min="6" max="6" width="17.29"/>
+    <col customWidth="1" min="7" max="10" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
@@ -2491,51 +2527,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
         <v>0.0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="2">
         <v>0.0</v>
       </c>
-      <c r="E2" s="2">
-        <v>-1.0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>-1.0</v>
+      <c r="E2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.0</v>
       </c>
       <c r="G2" s="2">
         <v>-1.0</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
+      <c r="H2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1.0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1"/>
